--- a/02_DIA_inicio_2026_analisis_assets/rbd_9703_escuela-esperanza-joven_nt2_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9703_escuela-esperanza-joven_nt2_rubricas.xlsx
@@ -1980,13 +1980,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A341C2DA-ED0C-43B6-8F3E-1535E67026E3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57F35186-E684-4145-97B5-185A465DB059}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18AAD333-DFA4-4571-AD75-62491B34F2D6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A05C447E-FCB4-4810-9587-3255473DE2F5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89CF8436-CEA7-4F51-A98D-55D55FCD0C95}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0954A18F-705B-475E-B5CC-766B9F257979}"/>
 </file>